--- a/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>NVST</t>
   </si>
@@ -656,475 +656,487 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44106</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44015</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43924</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43644</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43553</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43371</v>
       </c>
-      <c r="AI7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>730500</v>
+      </c>
+      <c r="E8" s="3">
         <v>705500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>750600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>669900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>682100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>616900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>652900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>601000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>633100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>623600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>645600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>631300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>662400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>627200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>660800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>631100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>645800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>631400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>651800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>607300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1249800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>612600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>616300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>547200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>765600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>547200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>720500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>659300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2083900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>659700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1438500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>679500</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E9" s="3">
         <v>312300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>337500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>294800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>311900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>279600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>283600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>303200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>265600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>307000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>267000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>279000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>263000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>291000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>263000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>269100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>257600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>268800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>250000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>516900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>251300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>268300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>235500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>352200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>266000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>331100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>292300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>440700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>296600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>298600</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>401700</v>
+      </c>
+      <c r="E10" s="3">
         <v>393200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>413100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>375100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>370200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>337900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>373300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>317400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>329900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>358000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>338600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>364300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>383400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>364200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>369800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>368100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>376700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>373800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>383000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>357300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>732900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>361300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>348000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>311700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>413400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>281200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>389400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>367000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1643200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>363100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1436200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>380900</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1162,115 +1174,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E12" s="3">
         <v>30000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>28300</v>
       </c>
       <c r="G12" s="3">
         <v>28300</v>
       </c>
       <c r="H12" s="3">
+        <v>28300</v>
+      </c>
+      <c r="I12" s="3">
         <v>25300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>51700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>25800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>23200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>20000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>43500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>34700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>35400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>36300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>139100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>43300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>36000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>42300</v>
       </c>
-      <c r="AI12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1376,104 +1392,107 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E14" s="3">
         <v>7100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1161100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>272000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>39100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>58800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>57400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>39100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>51900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1950500</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1943600</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1483,53 +1502,56 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E15" s="3">
         <v>29200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>36400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1590,8 +1612,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1626,222 +1651,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>654600</v>
+      </c>
+      <c r="E17" s="3">
         <v>635900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>670000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>605100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>631300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>567600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>593300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>578500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>626800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>568600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>577200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>541200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>569900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>550800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>572800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>556600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>580600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>539900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>605700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>525600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1071400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>517500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>542800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>485600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>857200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>572200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>642500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>580600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>735600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>614800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>115300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>598100</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E18" s="3">
         <v>69600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>80600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>64800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>50800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>49300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>59600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>55000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>68400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>90100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>92500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>76400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>88000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>74500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>65200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>91500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>81700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>178400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>95100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>73500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>61600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-91600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>78000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>78700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1348300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>44900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1323200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>81400</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1879,55 +1911,56 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>-200</v>
       </c>
       <c r="P20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
@@ -1936,263 +1969,269 @@
         <v>300</v>
       </c>
       <c r="U20" s="3">
+        <v>300</v>
+      </c>
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
       </c>
       <c r="AB20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1017100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1500</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E21" s="3">
         <v>95900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>104200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>95400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>83000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>76500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>88500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>87200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>103800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>123100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>126200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>125900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>110500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>123100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>79300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>112000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>240900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>126700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>105200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>96400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-26500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>109300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>156200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>318700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>77300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="3">
         <v>160300</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E22" s="3">
         <v>7400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17800</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>3300</v>
       </c>
       <c r="AC22" s="3">
         <v>3300</v>
       </c>
       <c r="AD22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>99400</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>115300</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="s">
-        <v>3</v>
+      <c r="AI22" s="3">
+        <v>0</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>3</v>
@@ -2200,222 +2239,231 @@
       <c r="AK22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E23" s="3">
         <v>52200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>57600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>49900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>36500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1166100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>35300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-215000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>35800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>68600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>55700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>75700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>63200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>59100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>85900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>69900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>147400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>77400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>50800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-109200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>74600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>78700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>231800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>45000</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI23" s="3">
         <v>82900</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E24" s="3">
         <v>13500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>80200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>35300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-14500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-10300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-40300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-37000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>115300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18800</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2521,222 +2569,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E26" s="3">
         <v>38700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1151600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-217400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>51900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>43800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>73500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>44500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>70400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>80200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>140800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>61800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>91100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-72200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>56100</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>62100</v>
       </c>
       <c r="AE26" s="3">
         <v>62100</v>
       </c>
       <c r="AF26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>37900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>154600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>64100</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E27" s="3">
         <v>38700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1151600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-217400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>51900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>43800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>73500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>49600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>44500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>70400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>80200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>140800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>61800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>91100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-72200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>56100</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>62100</v>
       </c>
       <c r="AE27" s="3">
         <v>62100</v>
       </c>
       <c r="AF27" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>37900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>154600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>64100</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2842,8 +2899,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,40 +2950,40 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-2000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>2600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>4500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>43300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>12700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>21000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>9900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>17300</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>12000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-38500</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2949,8 +3009,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3056,8 +3119,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3163,55 +3229,58 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>200</v>
       </c>
       <c r="P32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
@@ -3220,165 +3289,171 @@
         <v>-300</v>
       </c>
       <c r="U32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1017100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E33" s="3">
         <v>38700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1151600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-217400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>51900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>43800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>73500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>47600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>74900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>85800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>92900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>161800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>71700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>108400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>56100</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>62100</v>
       </c>
       <c r="AE33" s="3">
         <v>62100</v>
       </c>
       <c r="AF33" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>37900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>154600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>64100</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3484,227 +3559,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E35" s="3">
         <v>38700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1151600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-217400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>51900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>43800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>73500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>47600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>74900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>85800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>92900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>161800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>71700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>108400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>56100</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>62100</v>
       </c>
       <c r="AE35" s="3">
         <v>62100</v>
       </c>
       <c r="AF35" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>37900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>154600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>64100</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44106</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44015</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43924</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43644</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43553</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43371</v>
       </c>
-      <c r="AI38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3742,8 +3826,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3781,95 +3866,96 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1125600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1082800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1211700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1133900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1110600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1077300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1069100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>991300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1036200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>948500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>940000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>824200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>651700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>585200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>606900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>568500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>523100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1078300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1073600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>638800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>553900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>441200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>888900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>822400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>353600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>211200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>193200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3888,8 +3974,11 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3995,98 +4084,101 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>436900</v>
+      </c>
+      <c r="E43" s="3">
         <v>436600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>429600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>405900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>422800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>393100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>363000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>392100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>380600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>413000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>407500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>417100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>415200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>401800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>393500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>392200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>372800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>342600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>331900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>307400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>355000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>358100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>361000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>365400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>306400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>365900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>443600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>456400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3602200</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4102,98 +4194,101 @@
       <c r="AK43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>290900</v>
+      </c>
+      <c r="E44" s="3">
         <v>300300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>288100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>290800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>281900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>261300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>241000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>265600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>263800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>267400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>258800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>278800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>297000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>307200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>300800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>291300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>286000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>280400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>263800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>274300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>311500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>283200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>266900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>257500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>280800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>312300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>277900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>278400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1624300</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4304,11 @@
       <c r="AK44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4235,12 +4333,12 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,54 +4351,54 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>123400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>114000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>206400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>207600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>166500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>545900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>81300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>80800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>73700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>92500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>108100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>82400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>69200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>50500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1328700</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4316,98 +4414,101 @@
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1919100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2026600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1948300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1934900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1849700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1788300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1797000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1821900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1771900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1743700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1640700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1488900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1414300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1424600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1366000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1388300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1908900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1835800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1766400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1301700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1163300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1590500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1416200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1517700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1114200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1001900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>978500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6009000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,8 +4524,11 @@
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4432,29 +4536,29 @@
         <v>26400</v>
       </c>
       <c r="E47" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F47" s="3">
         <v>28800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>28700</v>
       </c>
       <c r="G47" s="3">
         <v>28700</v>
       </c>
       <c r="H47" s="3">
+        <v>28700</v>
+      </c>
+      <c r="I47" s="3">
         <v>27100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>26700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4467,8 +4571,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4497,32 +4601,32 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="3">
         <v>22300</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF47" s="3">
         <v>4938800</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -4530,98 +4634,101 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>441900</v>
+      </c>
+      <c r="E48" s="3">
         <v>442300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>438900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>436400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>428900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>418400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>419800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>433200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>415800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>431500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>434700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>430600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>429700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>430500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>425400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>409300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>394600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>391200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>392200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>416900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>457800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>451200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>468300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>473900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>483200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>482600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>490400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>484900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17317700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4637,98 +4744,101 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2966800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2992800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2985400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3008500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3035700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2953600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2911800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3029900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2981800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4178500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4246200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4459600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4536900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4571900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4583300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4463400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4465700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4097300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4178400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4204600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4574800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4580400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4689900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4642900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4589100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4551100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4591600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4574300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>623900</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4744,8 +4854,11 @@
       <c r="AK49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4851,8 +4964,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4958,98 +5074,101 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E52" s="3">
         <v>197400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>220600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>236200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>217600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>250600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>191900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>174400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>180500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>152900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>151700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>158300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>153700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>173200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>212400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>174900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>167800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>174100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>147000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>127000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>127300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>72700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>75200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>70700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>74400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>80700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>626800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5065,8 +5184,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5172,98 +5294,101 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5597100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5578000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5679000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5642500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5664400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5466400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5350500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5510700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5438100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6556300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6605100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6683800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6607200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6575000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6587000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6411900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6461000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6572300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6574200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6562000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6481300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6321900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6876000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6605700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6665200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6240900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6158300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6118400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>154600</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5279,8 +5404,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5318,8 +5446,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5357,95 +5486,96 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>190200</v>
+      </c>
+      <c r="E57" s="3">
         <v>170000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>191600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>156000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>171800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>163500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>174600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>172100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>172400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>174700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>179500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>168600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>176800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>186800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>228300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>190000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>182700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>180600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>185800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>171000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>209400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>204600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>235100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>161100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>130900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>194800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>208000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>181400</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5464,95 +5594,98 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E58" s="3">
         <v>38700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>39000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>39200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>36100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>151000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>152000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>150200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>148000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>145600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>144500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>540000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>539200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>510000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>579300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>508600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>507800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>432400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>426700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>421500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>416400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>886800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>253500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>152000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5571,98 +5704,101 @@
       <c r="AK58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E59" s="3">
         <v>370900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>359100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>384900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>370100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>359300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>317200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>314200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>301200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>286000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>257900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>236700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>250600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>252700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>498400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>489000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>564900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>567300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>590000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>671500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>532300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>515300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>562800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>514000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>445800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>410600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>497300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>427300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5070100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5678,98 +5814,101 @@
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>807300</v>
+      </c>
+      <c r="E60" s="3">
         <v>786600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>852600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>821700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>793900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>873300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>878700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>865500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>821400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>781300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>780800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>746800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1150800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1149600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1236700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1258300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1256200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1255700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1208200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1269200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1163200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1136300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1684700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>678900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>830200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>608900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>709200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>760700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17300</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5785,98 +5924,101 @@
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1549500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1550500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1558700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1562900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1560100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1409500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1397200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1423000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1492500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1498000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1508000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1493300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>992400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>995100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>870700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>851600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>864100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>876900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>883400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>887800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>893200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>892200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>907700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1755500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1722200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1546700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1321000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1304500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5892,98 +6034,101 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E62" s="3">
         <v>98800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>100300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>112500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>114800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>96300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>89800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>103800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>104100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>103700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>103900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>127100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>128100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>126800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>272700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>344100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>324700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>408800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>424600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>457900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>556000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>546100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>562600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>611500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>616900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>599000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>585300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>539200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>329200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5999,8 +6144,11 @@
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6106,8 +6254,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6213,8 +6364,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6320,95 +6474,98 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2520800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2498500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2572700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2554300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2525400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2430300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2415700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2438200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2461400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2416000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2431200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2390600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2296200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2296000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2380100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2454000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2445000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2541400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2516600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2615300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2612800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2575000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3155400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3048100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3171800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2757200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2618100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2607100</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6427,8 +6584,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6466,8 +6626,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6573,8 +6734,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6680,8 +6844,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6787,8 +6954,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6894,95 +7064,98 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-348000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-401700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-440400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-473300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-443000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-469400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-487400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-488600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-496800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>654800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>631200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>848600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>827100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>775200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>731400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>657900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>610300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>563200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>466900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>381100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>288200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>198100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>126400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>75900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>93100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>37000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7001,8 +7174,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7108,8 +7284,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7215,8 +7394,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7322,95 +7504,98 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3076300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3079500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3106300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3088200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3139000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3036100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2934800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3072500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2976700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4140300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4173900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4293200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4311000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4279000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4206900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3957900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4016000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4030900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4057600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3946700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3868500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3746900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3720600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3557600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3493400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3483700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3540200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3511300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7429,8 +7614,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7536,227 +7724,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44106</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44015</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43924</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43644</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43553</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43371</v>
       </c>
-      <c r="AI80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E81" s="3">
         <v>38700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1151600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-217400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>51900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>43800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>73500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>47600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>74900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>85800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>92900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>161800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>71700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>108400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>56100</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>62100</v>
       </c>
       <c r="AE81" s="3">
         <v>62100</v>
       </c>
       <c r="AF81" s="3">
+        <v>62100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>37900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>154600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>64100</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7794,115 +7991,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E83" s="3">
         <v>9100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>14200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>35700</v>
       </c>
       <c r="R83" s="3">
         <v>35700</v>
       </c>
       <c r="S83" s="3">
+        <v>35700</v>
+      </c>
+      <c r="T83" s="3">
         <v>35100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>30100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>61900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>33100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>34600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>64900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>77300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>77400</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8008,8 +8209,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8115,8 +8319,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8222,8 +8429,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8329,8 +8539,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8436,115 +8649,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>108000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>78700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>88700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>132400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>70700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>93100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>102000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>95500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>75100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>110300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>46700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>136000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>88300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>137300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>16600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>193400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>148100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-57600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-62300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>187000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>281300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-61800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-225200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>210500</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8582,106 +8801,107 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>8900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-225200</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
@@ -8689,8 +8909,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8796,8 +9019,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8903,115 +9129,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-68900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-69700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-591600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>288600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-51400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>15300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15300</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>58900</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9049,8 +9281,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9093,8 +9326,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9156,8 +9389,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9263,8 +9499,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9370,8 +9609,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9477,101 +9719,104 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-45600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-41700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>114500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-68300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>73700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-463100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-469600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-244400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>733100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>258500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-148100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3">
         <v>24300</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9584,100 +9829,103 @@
       <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E101" s="3">
         <v>34300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-46300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>15500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>23100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>13600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>10800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>3</v>
@@ -9691,100 +9939,103 @@
       <c r="AK101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-128900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>77800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-44900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>87700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>115800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>172500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>66500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>45400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-555200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>434800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>84900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-335000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-447700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>188100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-121600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>611200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>142400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
       </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
@@ -9796,6 +10047,9 @@
         <v>3</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
